--- a/prix/collecteur.xlsx
+++ b/prix/collecteur.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\caisse5\Desktop\site-internet\raccords-plomberie\prix\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\raccords-plomberie\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53F45168-546E-44D8-8E2C-ADA986C877A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAFCC145-D7B0-4AB3-856E-456116B1BA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{AC89CC73-BE36-4334-9D51-D90570969AD5}"/>
   </bookViews>
@@ -265,7 +265,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -298,9 +298,6 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -309,6 +306,12 @@
     </xf>
     <xf numFmtId="4" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -698,13 +701,13 @@
       <c r="C2" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="D2" s="12">
+      <c r="D2" s="16">
         <v>26.11</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="11">
+      <c r="F2" s="15">
         <v>10</v>
       </c>
     </row>
@@ -718,14 +721,14 @@
       <c r="C3" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="D3" s="12">
+      <c r="D3" s="16">
         <v>34.82</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="11">
-        <v>14</v>
+      <c r="F3" s="15">
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
@@ -738,14 +741,14 @@
       <c r="C4" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="16">
         <v>47.11</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E4" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="11">
-        <v>7</v>
+      <c r="F4" s="15">
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
@@ -758,14 +761,14 @@
       <c r="C5" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="16">
         <v>53.45</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="11">
-        <v>20</v>
+      <c r="F5" s="15">
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
@@ -778,13 +781,13 @@
       <c r="C6" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D6" s="12">
+      <c r="D6" s="16">
         <v>62.97</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="E6" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="11">
+      <c r="F6" s="15">
         <v>17</v>
       </c>
     </row>
@@ -798,13 +801,13 @@
       <c r="C7" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="D7" s="12">
+      <c r="D7" s="16">
         <v>23.46</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="E7" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="11">
+      <c r="F7" s="15">
         <v>15</v>
       </c>
     </row>
@@ -818,14 +821,14 @@
       <c r="C8" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="16">
         <v>34.82</v>
       </c>
-      <c r="E8" s="13" t="s">
+      <c r="E8" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="11">
-        <v>13</v>
+      <c r="F8" s="15">
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
@@ -838,13 +841,13 @@
       <c r="C9" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="D9" s="12">
+      <c r="D9" s="16">
         <v>44.27</v>
       </c>
-      <c r="E9" s="13" t="s">
+      <c r="E9" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="F9" s="11">
+      <c r="F9" s="15">
         <v>7</v>
       </c>
     </row>
@@ -858,13 +861,13 @@
       <c r="C10" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="16">
         <v>48.44</v>
       </c>
-      <c r="E10" s="13" t="s">
+      <c r="E10" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="F10" s="11">
+      <c r="F10" s="15">
         <v>12</v>
       </c>
     </row>
@@ -878,13 +881,13 @@
       <c r="C11" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="16">
         <v>62.97</v>
       </c>
-      <c r="E11" s="13" t="s">
+      <c r="E11" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="F11" s="11">
+      <c r="F11" s="15">
         <v>4</v>
       </c>
     </row>
@@ -898,10 +901,10 @@
       <c r="C12" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D12" s="15">
+      <c r="D12" s="14">
         <v>25.86</v>
       </c>
-      <c r="E12" s="14" t="s">
+      <c r="E12" s="13" t="s">
         <v>20</v>
       </c>
       <c r="F12" s="11">
@@ -918,10 +921,10 @@
       <c r="C13" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D13" s="15">
+      <c r="D13" s="14">
         <v>25.86</v>
       </c>
-      <c r="E13" s="14" t="s">
+      <c r="E13" s="13" t="s">
         <v>22</v>
       </c>
       <c r="F13" s="11">
@@ -938,10 +941,10 @@
       <c r="C14" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="D14" s="15">
+      <c r="D14" s="14">
         <v>56.47</v>
       </c>
-      <c r="E14" s="14" t="s">
+      <c r="E14" s="13" t="s">
         <v>24</v>
       </c>
       <c r="F14" s="11">
@@ -958,10 +961,10 @@
       <c r="C15" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="D15" s="15">
+      <c r="D15" s="14">
         <v>56.47</v>
       </c>
-      <c r="E15" s="14" t="s">
+      <c r="E15" s="13" t="s">
         <v>26</v>
       </c>
       <c r="F15" s="11">

--- a/prix/collecteur.xlsx
+++ b/prix/collecteur.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\raccords-plomberie\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAFCC145-D7B0-4AB3-856E-456116B1BA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08722741-C3E6-439D-92F5-7C6178E2E29F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{AC89CC73-BE36-4334-9D51-D90570969AD5}"/>
   </bookViews>
@@ -198,7 +198,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.000"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -222,6 +222,13 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -265,7 +272,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -307,10 +314,13 @@
     <xf numFmtId="4" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -707,7 +717,7 @@
       <c r="E2" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="15">
+      <c r="F2" s="17">
         <v>10</v>
       </c>
     </row>
@@ -727,7 +737,7 @@
       <c r="E3" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="15">
+      <c r="F3" s="17">
         <v>12</v>
       </c>
     </row>
@@ -747,7 +757,7 @@
       <c r="E4" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="15">
+      <c r="F4" s="17">
         <v>8</v>
       </c>
     </row>
@@ -767,8 +777,8 @@
       <c r="E5" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="15">
-        <v>19</v>
+      <c r="F5" s="17">
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
@@ -787,7 +797,7 @@
       <c r="E6" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="15">
+      <c r="F6" s="17">
         <v>17</v>
       </c>
     </row>
@@ -807,8 +817,8 @@
       <c r="E7" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="15">
-        <v>15</v>
+      <c r="F7" s="17">
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -827,8 +837,8 @@
       <c r="E8" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="15">
-        <v>10</v>
+      <c r="F8" s="17">
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
@@ -847,8 +857,8 @@
       <c r="E9" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="F9" s="15">
-        <v>7</v>
+      <c r="F9" s="17">
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
@@ -867,8 +877,8 @@
       <c r="E10" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="F10" s="15">
-        <v>12</v>
+      <c r="F10" s="17">
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
@@ -887,15 +897,15 @@
       <c r="E11" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="F11" s="15">
-        <v>4</v>
+      <c r="F11" s="17">
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="15" t="s">
         <v>21</v>
       </c>
       <c r="C12" s="7" t="s">
@@ -915,7 +925,7 @@
       <c r="A13" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="15" t="s">
         <v>23</v>
       </c>
       <c r="C13" s="7" t="s">
@@ -935,7 +945,7 @@
       <c r="A14" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="15" t="s">
         <v>25</v>
       </c>
       <c r="C14" s="7" t="s">
@@ -955,7 +965,7 @@
       <c r="A15" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="15" t="s">
         <v>27</v>
       </c>
       <c r="C15" s="7" t="s">

--- a/prix/collecteur.xlsx
+++ b/prix/collecteur.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\raccords-plomberie\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08722741-C3E6-439D-92F5-7C6178E2E29F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D6FE060-A3FB-49BC-B7F9-CEA0C09229FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{AC89CC73-BE36-4334-9D51-D90570969AD5}"/>
   </bookViews>
@@ -778,7 +778,7 @@
         <v>6</v>
       </c>
       <c r="F5" s="17">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
@@ -878,7 +878,7 @@
         <v>16</v>
       </c>
       <c r="F10" s="17">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
@@ -898,7 +898,7 @@
         <v>18</v>
       </c>
       <c r="F11" s="17">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">

--- a/prix/collecteur.xlsx
+++ b/prix/collecteur.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\raccords-plomberie\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D6FE060-A3FB-49BC-B7F9-CEA0C09229FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14D199A5-6F34-40C4-A1AD-D6F247F579D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{AC89CC73-BE36-4334-9D51-D90570969AD5}"/>
   </bookViews>
@@ -738,7 +738,7 @@
         <v>2</v>
       </c>
       <c r="F3" s="17">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
@@ -758,7 +758,7 @@
         <v>4</v>
       </c>
       <c r="F4" s="17">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
@@ -818,7 +818,7 @@
         <v>10</v>
       </c>
       <c r="F7" s="17">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -838,7 +838,7 @@
         <v>12</v>
       </c>
       <c r="F8" s="17">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
@@ -858,7 +858,7 @@
         <v>14</v>
       </c>
       <c r="F9" s="17">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
@@ -898,7 +898,7 @@
         <v>18</v>
       </c>
       <c r="F11" s="17">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">

--- a/prix/collecteur.xlsx
+++ b/prix/collecteur.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\raccords-plomberie\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14D199A5-6F34-40C4-A1AD-D6F247F579D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C9D217D-6599-4422-835B-5D0576BC54AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{AC89CC73-BE36-4334-9D51-D90570969AD5}"/>
+    <workbookView xWindow="23124" yWindow="12" windowWidth="19116" windowHeight="10884" xr2:uid="{AC89CC73-BE36-4334-9D51-D90570969AD5}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -272,7 +272,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -318,6 +318,9 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -752,13 +755,13 @@
         <v>35</v>
       </c>
       <c r="D4" s="16">
-        <v>47.11</v>
+        <v>49.27</v>
       </c>
       <c r="E4" s="12" t="s">
         <v>4</v>
       </c>
       <c r="F4" s="17">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
@@ -832,13 +835,13 @@
         <v>34</v>
       </c>
       <c r="D8" s="16">
-        <v>34.82</v>
+        <v>36.92</v>
       </c>
       <c r="E8" s="12" t="s">
         <v>12</v>
       </c>
       <c r="F8" s="17">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
@@ -852,13 +855,13 @@
         <v>35</v>
       </c>
       <c r="D9" s="16">
-        <v>44.27</v>
+        <v>49.27</v>
       </c>
       <c r="E9" s="12" t="s">
         <v>14</v>
       </c>
       <c r="F9" s="17">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
@@ -872,13 +875,13 @@
         <v>36</v>
       </c>
       <c r="D10" s="16">
-        <v>48.44</v>
+        <v>61.88</v>
       </c>
       <c r="E10" s="12" t="s">
         <v>16</v>
       </c>
       <c r="F10" s="17">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
@@ -892,13 +895,13 @@
         <v>37</v>
       </c>
       <c r="D11" s="16">
-        <v>62.97</v>
+        <v>72.88</v>
       </c>
       <c r="E11" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="F11" s="17">
-        <v>-1</v>
+      <c r="F11" s="18">
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
